--- a/samples/output/iic-as-built/reports/azlocal-iic-01-as-built-20260406T160832Z-delivery-registers.xlsx
+++ b/samples/output/iic-as-built/reports/azlocal-iic-01-as-built-20260406T160832Z-delivery-registers.xlsx
@@ -10,6 +10,15 @@
     <sheet name="AzureResources" sheetId="6" r:id="rId6"/>
     <sheet name="Findings" sheetId="7" r:id="rId7"/>
     <sheet name="Collectors" sheetId="8" r:id="rId8"/>
+    <sheet name="Extensions" sheetId="9" r:id="rId9"/>
+    <sheet name="LogicalNetworks" sheetId="10" r:id="rId10"/>
+    <sheet name="Subnets" sheetId="11" r:id="rId11"/>
+    <sheet name="StoragePaths" sheetId="12" r:id="rId12"/>
+    <sheet name="ResourceBridges" sheetId="13" r:id="rId13"/>
+    <sheet name="CustomLocations" sheetId="14" r:id="rId14"/>
+    <sheet name="ArcGateways" sheetId="15" r:id="rId15"/>
+    <sheet name="Images" sheetId="16" r:id="rId16"/>
+    <sheet name="CostLicensing" sheetId="17" r:id="rId17"/>
   </sheets>
 </workbook>
 </file>
@@ -201,6 +210,762 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">VmSwitch</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">DhcpEnabled</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">SubnetCount</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lnet-iic-mgmt-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConvergedSwitch</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lnet-iic-workload-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConvergedSwitch</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Network</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Subnet</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">AddressPrefix</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Vlan</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">IpPools</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lnet-iic-mgmt-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subnet-management</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.0.0.0/24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2203</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lnet-iic-workload-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">subnet-workload</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.0.2.0/24</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2205</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">AvailableGB</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">FileSystem</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sp-iic-vmstore-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\ClusterStorage\csv-iic-azlocal-01-vmstore-01\ArcVmDisks</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1480</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSVFS_ReFS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sp-iic-vmstore-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\ClusterStorage\csv-iic-azlocal-01-vmstore-02\ArcVmDisks</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1620</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSVFS_ReFS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sp-iic-vmstore-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C:\ClusterStorage\csv-iic-azlocal-01-vmstore-03\ArcVmDisks</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1710</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSVFS_ReFS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Version</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Distro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Provider</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Location</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rb-iic-azlocal-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connected</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5.23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOC-K8S</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HCI</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eastus</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Namespace</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Location</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cl-iic-azlocal-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azlocal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eastus</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Endpoint</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">AllowedFeatures</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">AllowedResources</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arcgw-iic-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://arcgw-iic-01.gw.arc.azure.com</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">*</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">OsType</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Publisher</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Sku</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Version</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">SizeGB</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">img-iic-ws2022-datacenter</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketplace</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Windows</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MicrosoftWindowsServer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2022-datacenter-azure-edition</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20348.2700.240906</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">img-iic-rhel9-base</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Custom</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Linux</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9.4.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Node</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">PhysicalCores</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">AhbEnabled</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">MonthlyCostUsd</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">MonthlySavingUsd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">320</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H4"/>
@@ -3073,4 +3838,384 @@
   </sheetData>
   <autoFilter ref="A1:E8"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Node</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Publisher</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Version</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ProvisioningState</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">AutoUpgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AzureMonitorWindowsAgent</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AzureMonitorWindowsAgent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.Azure.Monitor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.22.2.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GuestConfigExtension</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConfigurationforWindows</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.GuestConfiguration</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.29.78.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MicrosoftDefenderForServers</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDE.Windows</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.Azure.AzureDefenderForServers</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AzureMonitorWindowsAgent</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AzureMonitorWindowsAgent</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.Azure.Monitor</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.22.2.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GuestConfigExtension</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConfigurationforWindows</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.GuestConfiguration</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.29.78.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MicrosoftDefenderForServers</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDE.Windows</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.Azure.AzureDefenderForServers</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AzureMonitorWindowsAgent</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AzureMonitorWindowsAgent</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.Azure.Monitor</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.22.2.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GuestConfigExtension</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ConfigurationforWindows</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.GuestConfiguration</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.29.78.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">azl-iic-n03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MicrosoftDefenderForServers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDE.Windows</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft.Azure.AzureDefenderForServers</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Succeeded</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G10"/>
+</worksheet>
 </file>